--- a/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Collectible.xlsx
+++ b/PTBR-COM-PORTRAIT/Lang/PTBR/Game/Collectible.xlsx
@@ -805,7 +805,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Conta</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Flutuar</t>
+          <t>Salva-vidas</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Bastão Longo</t>
+          <t>Vareta Comprida</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1189,7 +1189,7 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lavanderia</t>
+          <t>Roupa Pendurada</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Fluído Corporal</t>
+          <t>Fluido Corporal</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1253,7 +1253,7 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Rã Voadora</t>
+          <t>Sapo Voador</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Conta Dourada</t>
+          <t>Boleto Dourado</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Cristal da Terra</t>
+          <t>Cristal de Terra</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cogumelo Caótico Dourado</t>
+          <t>Cogumelo do Caos Dourado</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Massinha Dourada</t>
+          <t>Putit Dourado</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>Massinha de Ouro</t>
+          <t>Putit Banhado a Ouro</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Urso de Pelúcia</t>
+          <t>Ursinho de Pelúcia</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2235,7 +2235,7 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Adaga Etérea</t>
+          <t>Adaga do Éter</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Vessel Dourado</t>
+          <t>Vesel Dourado</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>Androide</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2685,7 +2685,7 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Fragmento Mágico</t>
+          <t>Fragmento de Magia</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -2776,7 +2776,7 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Cão da Mina</t>
+          <t>Cão-Mina</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -2808,7 +2808,7 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Pedra Explosiva</t>
+          <t>Pedra-Bomba</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -2872,7 +2872,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Pintura de Retrato</t>
+          <t>Quadro de Retrato</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -2904,7 +2904,7 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Pintura Paisagem</t>
+          <t>Quadro de Paisagem</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3470,7 +3470,7 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Grande Tentáculo</t>
+          <t>Tentáculo Grande</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Enorme Tentáculo</t>
+          <t>Tentáculo Enorme</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -3529,7 +3529,7 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Último Chefe</t>
+          <t>Chefão Final</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -3652,7 +3652,7 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Tentáculo Louco</t>
+          <t>Tentáculo Enlouquecido</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -3684,7 +3684,7 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Cogumelo Caótico</t>
+          <t>Cogumelo do Caos</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Frango Mofu</t>
+          <t>Frango Felpudo</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
